--- a/templates/menu-template.xlsx
+++ b/templates/menu-template.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأقسام" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأصناف" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأحجام" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العروض" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإضافات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العروض" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -518,7 +519,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>١. املأ الأوراق بالترتيب: الأقسام ← الأصناف ← الأحجام ← العروض (العروض اختيارية).</t>
+          <t>١. املأ الأوراق بالترتيب: الأقسام ← الأصناف ← الأحجام ← الإضافات ← العروض (الإضافات والعروض اختيارية).</t>
         </is>
       </c>
     </row>
@@ -625,78 +626,95 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>العروض</t>
+          <t>الإضافات (اختياري)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>• نسبة خصم: القيمة من ١ لـ ٩٩، وبتتطبق على كل الأحجام.</t>
+          <t>• صف لكل إضافة: معرّف الصنف، والاسم، والسعر. لو صنف موجود في ورقة الإضافات، إضافاته بتتبدّل باللي في الملف.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>• خصم مبلغ: القيمة بتتطرح من سعر كل حجم، ولازم تكون أقل من أرخص سعر.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>• سعر جديد: لصنف بسعر واحد اكتب السعر الجديد. لصنف بأحجام اكتب صف لكل حجم فيه رمز الحجم والسعر الجديد.</t>
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>العروض</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>• توصيل مجاني: مفيش قيمة. عرض مكتوب: اكتب النص (مثلًا: اشتري ٢ والتالت هدية).</t>
+          <t>• نسبة خصم: القيمة من ١ لـ ٩٩، وبتتطبق على كل الأحجام.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>• تاريخ الانتهاء مطلوب بالشكل ده: 2026-12-31 23:59</t>
+          <t>• خصم مبلغ: القيمة بتتطرح من سعر كل حجم، ولازم تكون أقل من أرخص سعر.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>القيم المسموحة (فيه قوائم جاهزة في الخانات)</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>• سعر جديد: لصنف بسعر واحد اكتب السعر الجديد. لصنف بأحجام اكتب صف لكل حجم فيه رمز الحجم والسعر الجديد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>• توصيل مجاني: مفيش قيمة. عرض مكتوب: اكتب النص (مثلًا: اشتري ٢ والتالت هدية).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>نوع السعر: سعر واحد / أحجام — الإتاحة: متاح / غير متاح — نعم / لا</t>
+          <t>• تاريخ الانتهاء مطلوب بالشكل ده: 2026-12-31 23:59</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>نوع الخدمة: دليفري واستلام / دليفري فقط / استلام فقط</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>الأيقونة: قهوة، مشروبات، برجر، بيتزا، ساندوتشات، فراخ، مشويات، أسماك، سلطات، فطار، حلويات، أطباق</t>
+      <c r="A30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>القيم المسموحة (فيه قوائم جاهزة في الخانات)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>نوع السعر: سعر واحد / أحجام — الإتاحة: متاح / غير متاح — نعم / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>نوع الخدمة: دليفري واستلام / دليفري فقط / استلام فقط</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>الأيقونة: قهوة، مشروبات، برجر، بيتزا، ساندوتشات، فراخ، مشويات، أسماك، سلطات، فطار، حلويات، أطباق</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>الصور: رابط يبدأ بـ https:// (أو سيبها فاضية وارفع الصورة من لوحة الإدارة).</t>
         </is>
@@ -960,7 +978,7 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1031,7 +1049,7 @@
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>مميز؟</t>
+          <t>الأكثر طلبًا؟</t>
         </is>
       </c>
     </row>
@@ -1431,6 +1449,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>معرّف الصنف *</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>اسم الإضافة بالعربي *</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>اسم الإضافة بالإنجليزي</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>السعر *</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>addon_name_ar</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>addon_name_en</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>EX-P1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>وش زيادة</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Extra foam</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>EX-P2</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>جبنة زيادة</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Extra cheese</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
